--- a/docs/06_テスト項目書.xlsx
+++ b/docs/06_テスト項目書.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -567,22 +567,34 @@
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>関連文書</t>
+          <t>更新日</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>テスト計画書（ZCN-TP-001）</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>関連文書</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>テスト計画書（ZCN-TP-001）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>zcomic-next 全機能</t>
         </is>
@@ -3598,7 +3610,7 @@
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>1. http://192.168.40.26:8080 にアクセス
+          <t>1. http://192.168.40.99:8080 にアクセス
 2. 各操作を試す</t>
         </is>
       </c>
@@ -3683,7 +3695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4792,11 +4804,687 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>API ドキュメント / 外部アクセス (ST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>テストID</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>テスト工程</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>機能ID</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>機能名</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>テスト手順</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>実施日</t>
+        </is>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>実施者</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t>不具合ID</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>ST-Doc-01</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Swagger UI</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>正常系：/docs が開ける</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>API稼働</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>1. ブラウザで http://192.168.40.99:4000/docs を開く</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Swagger UI が表示され、全エンドポイントがリスト表示される。</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr"/>
+      <c r="K30" s="9" t="inlineStr"/>
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="9" t="inlineStr"/>
+      <c r="N30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>ST-Doc-02</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>Swagger UI</t>
+        </is>
+      </c>
+      <c r="F31" s="12" t="inlineStr">
+        <is>
+          <t>正常系：Try it out で login が実行できる</t>
+        </is>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>テストユーザー存在</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="inlineStr">
+        <is>
+          <t>1. /docs を開く
+2. POST /graphql 展開
+3. login サンプルを選び e,p を入力
+4. Execute</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>200 が返り、レスポンス body に user 情報。Set-Cookie で zc_token がセットされる。</t>
+        </is>
+      </c>
+      <c r="J31" s="11" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr"/>
+      <c r="L31" s="11" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr"/>
+      <c r="N31" s="12" t="inlineStr">
+        <is>
+          <t>Servers が「/」になっていること</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>ST-Doc-03</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>OpenAPI YAML/JSON</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>/openapi.yaml と /openapi.json で取得できる</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>API稼働</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>1. curl http://192.168.40.99:4000/openapi.yaml
+2. curl http://192.168.40.99:4000/openapi.json</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>YAML / JSON 形式で OpenAPI 3.1 仕様が返る。</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr"/>
+      <c r="K32" s="9" t="inlineStr"/>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="9" t="inlineStr"/>
+      <c r="N32" s="10" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>ST-Doc-04</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="inlineStr">
+        <is>
+          <t>Redoc 静的HTML</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
+          <t>オフラインでRedoc閲覧</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>docs/08_API仕様_redoc.html + openapi.yaml が同階層に存在</t>
+        </is>
+      </c>
+      <c r="H33" s="12" t="inlineStr">
+        <is>
+          <t>1. 08_API仕様_redoc.html をブラウザで開く</t>
+        </is>
+      </c>
+      <c r="I33" s="12" t="inlineStr">
+        <is>
+          <t>Redoc UI が表示される。</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr"/>
+      <c r="L33" s="11" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr"/>
+      <c r="N33" s="12" t="inlineStr">
+        <is>
+          <t>Redoc は CDN から読み込むのでネット接続必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>ST-Ext-01</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>F-01〜07</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>外部アクセス（DDNS）</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>dirs.synology.me 経由で全機能が動作する</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Synology DDNS とリバースプロキシ設定済み</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>1. 外部ネットワークから http://dirs.synology.me:8080/ を開く
+2. ログイン
+3. 一覧 → 詳細 → ビューワー</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>社内LANと同等に動作する。</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr"/>
+      <c r="K34" s="9" t="inlineStr"/>
+      <c r="L34" s="9" t="inlineStr"/>
+      <c r="M34" s="9" t="inlineStr"/>
+      <c r="N34" s="10" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>ST-Ext-02</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>相対URL動作確認</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>ビルド成果物に社内IPが焼き込まれていない</t>
+        </is>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Web再ビルド済（VITE_API_URL=空）</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>1. docker compose exec web sh -c 'grep -ro "192.168.40" /usr/share/nginx/html/assets/ | head -5'</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>何も出力されない（社内IPがJSバンドルに含まれていない）。</t>
+        </is>
+      </c>
+      <c r="J35" s="11" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr"/>
+      <c r="L35" s="11" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr"/>
+      <c r="N35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>ST-Ext-03</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>DevTools での Origin 確認</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>/graphql のリクエスト先がブラウザの URL と一致</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>1. http://dirs.synology.me:8080/ にアクセス
+2. DevTools Network で /graphql の URL を確認</t>
+        </is>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>http://dirs.synology.me:8080/graphql に飛ぶ（社内IPには飛ばない）。</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr"/>
+      <c r="K36" s="9" t="inlineStr"/>
+      <c r="L36" s="9" t="inlineStr"/>
+      <c r="M36" s="9" t="inlineStr"/>
+      <c r="N36" s="10" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>新着順 SQL 仕様確認 (ST)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>テストID</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>テスト工程</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>機能ID</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>機能名</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>テスト観点</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>前提条件</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>テスト手順</t>
+        </is>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>実施日</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>実施者</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>不具合ID</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>ST-Sort-01</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>新着順並び</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>MAX(bok_mid) DESC でソートされる</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>tb_bok に異なる bok_mid の巻を含む作品が10件以上</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>1. /一覧を開く
+2. 1ページ目の各作品で MAX(bok_mid) を確認</t>
+        </is>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>並びが MAX(bok_mid) の降順になっている。</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr"/>
+      <c r="K40" s="9" t="inlineStr"/>
+      <c r="L40" s="9" t="inlineStr"/>
+      <c r="M40" s="9" t="inlineStr"/>
+      <c r="N40" s="10" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>ST-Sort-02</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="E41" s="12" t="inlineStr">
+        <is>
+          <t>vch9='comic' フィルタ</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
+          <t>comic以外は表示されない</t>
+        </is>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>tb_bok に vch9='comic' 以外の行を1件以上挿入</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="inlineStr">
+        <is>
+          <t>1. /一覧で表示確認</t>
+        </is>
+      </c>
+      <c r="I41" s="12" t="inlineStr">
+        <is>
+          <t>vch9='comic' のみ表示。</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr"/>
+      <c r="L41" s="11" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr"/>
+      <c r="N41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>ST-Sort-03</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>F-03</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>日本語キーグループ化</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>同じ (vch6, vch7) は1作品として集約</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>同じ著者・タイトルの巻が複数</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>1. /一覧確認</t>
+        </is>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>作品単位で1カードに集約され、最新巻のサムネが代表として表示。</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr"/>
+      <c r="K42" s="9" t="inlineStr"/>
+      <c r="L42" s="9" t="inlineStr"/>
+      <c r="M42" s="9" t="inlineStr"/>
+      <c r="N42" s="10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A8:N8"/>
+    <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A38:N38"/>
+    <mergeCell ref="A28:N28"/>
     <mergeCell ref="A14:N14"/>
-    <mergeCell ref="A22:N22"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
